--- a/Georgia_ECE_District_Contacts_2026-04-01.xlsx
+++ b/Georgia_ECE_District_Contacts_2026-04-01.xlsx
@@ -39,7 +39,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,11 @@
         <fgColor rgb="00DEEAF1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -79,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -103,6 +108,18 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,22 +487,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:Q134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4805,6 +4826,3102 @@
       <c r="M78" s="8" t="inlineStr">
         <is>
           <t>Small east Georgia district. Director name not confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>Bacon County School District</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>1300150</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Bacon</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>102 W. 4th Street, Alma, GA 31510</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr"/>
+      <c r="H79" s="9" t="inlineStr"/>
+      <c r="I79" s="9" t="inlineStr"/>
+      <c r="J79" s="9" t="inlineStr"/>
+      <c r="K79" s="9" t="inlineStr"/>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>(229) 632-5525</t>
+        </is>
+      </c>
+      <c r="M79" s="9" t="inlineStr"/>
+      <c r="N79" s="9" t="inlineStr"/>
+      <c r="O79" s="10" t="inlineStr"/>
+      <c r="P79" s="9" t="inlineStr">
+        <is>
+          <t>https://www.bcraiders.com/</t>
+        </is>
+      </c>
+      <c r="Q79" s="10" t="inlineStr">
+        <is>
+          <t>Bacon County Primary School serves PreK-2. Need to contact district for ECE director and curriculum details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>Banks County School District</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>1300240</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>1989 Historic Homer Hwy, Commerce, GA 30529</t>
+        </is>
+      </c>
+      <c r="G80" s="11" t="inlineStr"/>
+      <c r="H80" s="11" t="inlineStr"/>
+      <c r="I80" s="11" t="inlineStr"/>
+      <c r="J80" s="11" t="inlineStr"/>
+      <c r="K80" s="11" t="inlineStr"/>
+      <c r="L80" s="11" t="inlineStr">
+        <is>
+          <t>706-677-2224</t>
+        </is>
+      </c>
+      <c r="M80" s="11" t="inlineStr"/>
+      <c r="N80" s="11" t="inlineStr"/>
+      <c r="O80" s="12" t="inlineStr"/>
+      <c r="P80" s="11" t="inlineStr">
+        <is>
+          <t>https://www.banks.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q80" s="12" t="inlineStr">
+        <is>
+          <t>Banks County Primary School serves PreK. Staff directory available at district website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>Bleckley County School District</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>1300440</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Bleckley</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>2623</v>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>1050 Peter Street, Cochran, GA 31014</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr"/>
+      <c r="H81" s="9" t="inlineStr"/>
+      <c r="I81" s="9" t="inlineStr"/>
+      <c r="J81" s="9" t="inlineStr"/>
+      <c r="K81" s="9" t="inlineStr"/>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>(478) 934-2821</t>
+        </is>
+      </c>
+      <c r="M81" s="9" t="inlineStr"/>
+      <c r="N81" s="9" t="inlineStr"/>
+      <c r="O81" s="10" t="inlineStr"/>
+      <c r="P81" s="9" t="inlineStr">
+        <is>
+          <t>https://www.bleckley.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q81" s="10" t="inlineStr">
+        <is>
+          <t>Bleckley County Primary School (242 E. Dykes Street, Cochran, GA 31014) has 689 students PreK-2. Superintendent: Dr. Trey Belflower.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>Brantley County School District</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>1300480</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>Brantley</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>272 School Circle, Nahunta, GA 31553</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr"/>
+      <c r="H82" s="11" t="inlineStr"/>
+      <c r="I82" s="11" t="inlineStr"/>
+      <c r="J82" s="11" t="inlineStr"/>
+      <c r="K82" s="11" t="inlineStr"/>
+      <c r="L82" s="11" t="inlineStr">
+        <is>
+          <t>(912) 462-6176</t>
+        </is>
+      </c>
+      <c r="M82" s="11" t="inlineStr"/>
+      <c r="N82" s="11" t="inlineStr"/>
+      <c r="O82" s="12" t="inlineStr"/>
+      <c r="P82" s="11" t="inlineStr">
+        <is>
+          <t>https://www.brantley.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q82" s="12" t="inlineStr">
+        <is>
+          <t>Superintendent: Dr. Kim Morgan. Central office directory available on website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>Brooks County School District</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>1300540</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>Brooks</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>2192</v>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>1081 Barwick Road, Quitman, GA 31643</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr"/>
+      <c r="H83" s="9" t="inlineStr"/>
+      <c r="I83" s="9" t="inlineStr"/>
+      <c r="J83" s="9" t="inlineStr"/>
+      <c r="K83" s="9" t="inlineStr"/>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>(229) 263-7531</t>
+        </is>
+      </c>
+      <c r="M83" s="9" t="inlineStr"/>
+      <c r="N83" s="9" t="inlineStr"/>
+      <c r="O83" s="10" t="inlineStr">
+        <is>
+          <t>Early Learning Center for PreK students mentioned</t>
+        </is>
+      </c>
+      <c r="P83" s="9" t="inlineStr">
+        <is>
+          <t>https://www.brooks.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q83" s="10" t="inlineStr">
+        <is>
+          <t>District has dedicated Early Learning Center for PreK. Minority enrollment 70%, 92.8% economically disadvantaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>Calhoun County School District</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>1300750</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>Calhoun</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>439</v>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>10877 Dickey Street, Morgan, GA 39866</t>
+        </is>
+      </c>
+      <c r="G84" s="11" t="inlineStr"/>
+      <c r="H84" s="11" t="inlineStr"/>
+      <c r="I84" s="11" t="inlineStr"/>
+      <c r="J84" s="11" t="inlineStr"/>
+      <c r="K84" s="11" t="inlineStr"/>
+      <c r="L84" s="11" t="inlineStr">
+        <is>
+          <t>(229) 849-2765</t>
+        </is>
+      </c>
+      <c r="M84" s="11" t="inlineStr">
+        <is>
+          <t>Georgia Standards of Excellence (GSE)</t>
+        </is>
+      </c>
+      <c r="N84" s="11" t="inlineStr"/>
+      <c r="O84" s="12" t="inlineStr"/>
+      <c r="P84" s="11" t="inlineStr">
+        <is>
+          <t>https://www.calhoun.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q84" s="12" t="inlineStr">
+        <is>
+          <t>Very small district (3 schools). Superintendent: Michael H. Ward. Serves PreK-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>Charlton County School District</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>1300990</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>Charlton</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>1681</v>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>37 Touchdown Lane, Folkston, GA 31537</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr"/>
+      <c r="H85" s="9" t="inlineStr"/>
+      <c r="I85" s="9" t="inlineStr"/>
+      <c r="J85" s="9" t="inlineStr"/>
+      <c r="K85" s="9" t="inlineStr"/>
+      <c r="L85" s="9" t="inlineStr">
+        <is>
+          <t>(912) 496-2596</t>
+        </is>
+      </c>
+      <c r="M85" s="9" t="inlineStr"/>
+      <c r="N85" s="9" t="inlineStr"/>
+      <c r="O85" s="10" t="inlineStr"/>
+      <c r="P85" s="9" t="inlineStr">
+        <is>
+          <t>https://www.charlton.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q85" s="10" t="inlineStr">
+        <is>
+          <t>Superintendent: Dr. Brent Tilley. St. George Elementary offers PreK-6. Four schools total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>Chattahoochee County School District</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>1301050</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>Chattahoochee</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>962</v>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>326 Broad Street, Cusseta, GA 31805</t>
+        </is>
+      </c>
+      <c r="G86" s="11" t="inlineStr"/>
+      <c r="H86" s="11" t="inlineStr"/>
+      <c r="I86" s="11" t="inlineStr"/>
+      <c r="J86" s="11" t="inlineStr"/>
+      <c r="K86" s="11" t="inlineStr"/>
+      <c r="L86" s="11" t="inlineStr">
+        <is>
+          <t>(706) 989-3774</t>
+        </is>
+      </c>
+      <c r="M86" s="11" t="inlineStr"/>
+      <c r="N86" s="11" t="inlineStr"/>
+      <c r="O86" s="12" t="inlineStr">
+        <is>
+          <t>Head Start program available for eligible 3-4 year olds</t>
+        </is>
+      </c>
+      <c r="P86" s="11" t="inlineStr">
+        <is>
+          <t>https://www.chattahoochee.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q86" s="12" t="inlineStr">
+        <is>
+          <t>Chattahoochee County Education Center (PreK-5) has 276-330 students. Head Start partnership for young learners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>Chattooga County School District</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>1301080</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>Chattooga</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>2685</v>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>33 Middle School Road, Summerville, GA 30747</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
+      <c r="I87" s="9" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr"/>
+      <c r="L87" s="9" t="inlineStr">
+        <is>
+          <t>(706) 857-3447</t>
+        </is>
+      </c>
+      <c r="M87" s="9" t="inlineStr"/>
+      <c r="N87" s="9" t="inlineStr"/>
+      <c r="O87" s="10" t="inlineStr"/>
+      <c r="P87" s="9" t="inlineStr">
+        <is>
+          <t>https://www.chattooga.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q87" s="10" t="inlineStr">
+        <is>
+          <t>Superintendent: Dr. Michelle Helie. Summerville Pre-K at 206 Penn Street, Summerville, GA 30747. Five schools total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>Clay County School District</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>1301200</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>205</v>
+      </c>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>105 Washington Street, Fort Gaines, GA 39851</t>
+        </is>
+      </c>
+      <c r="G88" s="11" t="inlineStr"/>
+      <c r="H88" s="11" t="inlineStr"/>
+      <c r="I88" s="11" t="inlineStr"/>
+      <c r="J88" s="11" t="inlineStr"/>
+      <c r="K88" s="11" t="inlineStr"/>
+      <c r="L88" s="11" t="inlineStr">
+        <is>
+          <t>(229) 768-2232</t>
+        </is>
+      </c>
+      <c r="M88" s="11" t="inlineStr"/>
+      <c r="N88" s="11" t="inlineStr"/>
+      <c r="O88" s="12" t="inlineStr">
+        <is>
+          <t>Very small enrollment, high poverty area</t>
+        </is>
+      </c>
+      <c r="P88" s="11" t="inlineStr">
+        <is>
+          <t>https://www.clay.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q88" s="12" t="inlineStr">
+        <is>
+          <t>Smallest district (2 schools). 21 PreK students (11% of total). 100% minority enrollment, 100% economically disadvantaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>Colquitt County School District</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>1301380</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Colquitt</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>8844</v>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>710 Lane Street, Moultrie, GA 31768</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>Allen Edwards</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>Chief Academic Officer/Pre-K Director</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="inlineStr"/>
+      <c r="K89" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L89" s="9" t="inlineStr">
+        <is>
+          <t>(229) 890-6200</t>
+        </is>
+      </c>
+      <c r="M89" s="9" t="inlineStr"/>
+      <c r="N89" s="9" t="inlineStr"/>
+      <c r="O89" s="10" t="inlineStr">
+        <is>
+          <t>Dedicated Pre-K director position | 13 schools | Largest district in batch</t>
+        </is>
+      </c>
+      <c r="P89" s="9" t="inlineStr">
+        <is>
+          <t>https://www.colquitt.k12.ga.us/departments/pre-k/index</t>
+        </is>
+      </c>
+      <c r="Q89" s="10" t="inlineStr">
+        <is>
+          <t>Dedicated Pre-K department. Dr. Allen Edwards identified as CAO/Pre-K Director. Large district with multiple elementary schools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>Cook County School District</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>1301470</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>3068</v>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>37 Josey Road, Adel, GA 31620</t>
+        </is>
+      </c>
+      <c r="G90" s="11" t="inlineStr"/>
+      <c r="H90" s="11" t="inlineStr"/>
+      <c r="I90" s="11" t="inlineStr"/>
+      <c r="J90" s="11" t="inlineStr"/>
+      <c r="K90" s="11" t="inlineStr"/>
+      <c r="L90" s="11" t="inlineStr">
+        <is>
+          <t>(229) 896-2294</t>
+        </is>
+      </c>
+      <c r="M90" s="11" t="inlineStr"/>
+      <c r="N90" s="11" t="inlineStr"/>
+      <c r="O90" s="12" t="inlineStr">
+        <is>
+          <t>Cook Primary School serves PK-2 with 811 students</t>
+        </is>
+      </c>
+      <c r="P90" s="11" t="inlineStr">
+        <is>
+          <t>https://www.cook.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q90" s="12" t="inlineStr">
+        <is>
+          <t>Cook Primary School is dedicated PreK-2 school. Four schools total in district.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>Crisp County School District</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>1301560</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>Crisp</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>3442</v>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>201 7th Street South, Cordele, GA 31015</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
+      <c r="I91" s="9" t="inlineStr"/>
+      <c r="J91" s="9" t="inlineStr"/>
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr">
+        <is>
+          <t>(229) 276-3400</t>
+        </is>
+      </c>
+      <c r="M91" s="9" t="inlineStr"/>
+      <c r="N91" s="9" t="inlineStr"/>
+      <c r="O91" s="10" t="inlineStr">
+        <is>
+          <t>Dedicated Pre-K school with 222 students | Strategic PreK structure</t>
+        </is>
+      </c>
+      <c r="P91" s="9" t="inlineStr">
+        <is>
+          <t>https://www.crispschools.org/</t>
+        </is>
+      </c>
+      <c r="Q91" s="10" t="inlineStr">
+        <is>
+          <t>Dedicated Crisp County Pre-K school (grades PK only) with 222 students. Five schools total. Primary School grades K-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>Dade County School District</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>1301590</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>Dade</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>2043</v>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>52 Tradition Lane, Trenton, GA 30752</t>
+        </is>
+      </c>
+      <c r="G92" s="11" t="inlineStr"/>
+      <c r="H92" s="11" t="inlineStr"/>
+      <c r="I92" s="11" t="inlineStr"/>
+      <c r="J92" s="11" t="inlineStr"/>
+      <c r="K92" s="11" t="inlineStr"/>
+      <c r="L92" s="11" t="inlineStr">
+        <is>
+          <t>(706) 657-4361</t>
+        </is>
+      </c>
+      <c r="M92" s="11" t="inlineStr"/>
+      <c r="N92" s="11" t="inlineStr"/>
+      <c r="O92" s="12" t="inlineStr"/>
+      <c r="P92" s="11" t="inlineStr">
+        <is>
+          <t>https://www.dadecountyschools.org/</t>
+        </is>
+      </c>
+      <c r="Q92" s="12" t="inlineStr">
+        <is>
+          <t>Four schools. Offers PreK registration. Davis Elementary on Sand Mountain, other schools in Trenton valley.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Decatur County School District</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>1301710</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>Decatur</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>4270</v>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>100 South West Street, Bainbridge, GA 39817</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr"/>
+      <c r="H93" s="9" t="inlineStr"/>
+      <c r="I93" s="9" t="inlineStr"/>
+      <c r="J93" s="9" t="inlineStr"/>
+      <c r="K93" s="9" t="inlineStr"/>
+      <c r="L93" s="9" t="inlineStr">
+        <is>
+          <t>(229) 248-2200</t>
+        </is>
+      </c>
+      <c r="M93" s="9" t="inlineStr"/>
+      <c r="N93" s="9" t="inlineStr"/>
+      <c r="O93" s="10" t="inlineStr"/>
+      <c r="P93" s="9" t="inlineStr">
+        <is>
+          <t>https://www.dcboe.com/</t>
+        </is>
+      </c>
+      <c r="Q93" s="10" t="inlineStr">
+        <is>
+          <t>Six schools. Serves Bainbridge area. 67.1% economically disadvantaged. Middle-sized district.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>Dodge County School District</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>1301770</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>Dodge</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>2785</v>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>720 College Street, Eastman, GA 31023</t>
+        </is>
+      </c>
+      <c r="G94" s="11" t="inlineStr"/>
+      <c r="H94" s="11" t="inlineStr"/>
+      <c r="I94" s="11" t="inlineStr"/>
+      <c r="J94" s="11" t="inlineStr"/>
+      <c r="K94" s="11" t="inlineStr"/>
+      <c r="L94" s="11" t="inlineStr">
+        <is>
+          <t>(478) 374-3783</t>
+        </is>
+      </c>
+      <c r="M94" s="11" t="inlineStr"/>
+      <c r="N94" s="11" t="inlineStr"/>
+      <c r="O94" s="12" t="inlineStr"/>
+      <c r="P94" s="11" t="inlineStr">
+        <is>
+          <t>https://dodge.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q94" s="12" t="inlineStr">
+        <is>
+          <t>District has dedicated Curriculum-Instruction department; staff directory requires login. PreK program exists at DCPS PreK school.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>Dooly County School District</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>1301800</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Dooly</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>1088</v>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>202 Cotton Street, Vienna, GA 31092</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr"/>
+      <c r="J95" s="9" t="inlineStr"/>
+      <c r="K95" s="9" t="inlineStr"/>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>(229) 268-4761</t>
+        </is>
+      </c>
+      <c r="M95" s="9" t="inlineStr"/>
+      <c r="N95" s="9" t="inlineStr"/>
+      <c r="O95" s="10" t="inlineStr"/>
+      <c r="P95" s="9" t="inlineStr">
+        <is>
+          <t>https://dooly.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q95" s="10" t="inlineStr">
+        <is>
+          <t>Small rural district with 1,088 total enrollment. PreK offered at elementary school level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>Echols County School District</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>1301950</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>Echols</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>895</v>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>216 Highway 129 North, Statenville, GA</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr"/>
+      <c r="H96" s="11" t="inlineStr"/>
+      <c r="I96" s="11" t="inlineStr"/>
+      <c r="J96" s="11" t="inlineStr"/>
+      <c r="K96" s="11" t="inlineStr"/>
+      <c r="L96" s="11" t="inlineStr"/>
+      <c r="M96" s="11" t="inlineStr"/>
+      <c r="N96" s="11" t="inlineStr"/>
+      <c r="O96" s="12" t="inlineStr"/>
+      <c r="P96" s="11" t="inlineStr">
+        <is>
+          <t>https://echols.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q96" s="12" t="inlineStr">
+        <is>
+          <t>Very small rural district with 895 students. Pre-K-8 building constructed 2009-2010. 45.8% Hispanic/Latino enrollment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>Elbert County School District</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>1302010</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Elbert</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>3076</v>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>200 Jackson Street, Elberton, GA 30635</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr"/>
+      <c r="H97" s="9" t="inlineStr"/>
+      <c r="I97" s="9" t="inlineStr"/>
+      <c r="J97" s="9" t="inlineStr"/>
+      <c r="K97" s="9" t="inlineStr"/>
+      <c r="L97" s="9" t="inlineStr"/>
+      <c r="M97" s="9" t="inlineStr"/>
+      <c r="N97" s="9" t="inlineStr"/>
+      <c r="O97" s="10" t="inlineStr"/>
+      <c r="P97" s="9" t="inlineStr">
+        <is>
+          <t>https://elbert.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q97" s="10" t="inlineStr">
+        <is>
+          <t>PreK offered through Paul J. Blackwell Learning Center (Head Start and Pre-K programs). 60% minority enrollment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>Evans County School District</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>1302070</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>Evans</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>1798</v>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>604 North Main Street, Claxton, GA 30417</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr"/>
+      <c r="H98" s="11" t="inlineStr"/>
+      <c r="I98" s="11" t="inlineStr"/>
+      <c r="J98" s="11" t="inlineStr"/>
+      <c r="K98" s="11" t="inlineStr"/>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>(912) 739-3544</t>
+        </is>
+      </c>
+      <c r="M98" s="11" t="inlineStr"/>
+      <c r="N98" s="11" t="inlineStr"/>
+      <c r="O98" s="12" t="inlineStr"/>
+      <c r="P98" s="11" t="inlineStr">
+        <is>
+          <t>https://evans.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q98" s="12" t="inlineStr">
+        <is>
+          <t>PreK offered at Claxton Elementary (grades PK-5). 70% minority enrollment, 71.2% economically disadvantaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>Fannin County School District</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>1302100</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>Fannin</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>2820</v>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>276 School Road, Blue Ridge, GA 30513</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr"/>
+      <c r="H99" s="9" t="inlineStr"/>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>Pre-K Program Director</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr"/>
+      <c r="K99" s="9" t="inlineStr"/>
+      <c r="L99" s="9" t="inlineStr">
+        <is>
+          <t>(706) 946-2004</t>
+        </is>
+      </c>
+      <c r="M99" s="9" t="inlineStr"/>
+      <c r="N99" s="9" t="inlineStr"/>
+      <c r="O99" s="10" t="inlineStr"/>
+      <c r="P99" s="9" t="inlineStr">
+        <is>
+          <t>https://fannin.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q99" s="10" t="inlineStr">
+        <is>
+          <t>Pre-K Program Director position identified but name not found in public records. 89.8% white student body.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>Grady County School District</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>1302460</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>Grady</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>4463</v>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>985 1st Street NW, Cairo, GA 39828</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr"/>
+      <c r="H100" s="11" t="inlineStr"/>
+      <c r="I100" s="11" t="inlineStr"/>
+      <c r="J100" s="11" t="inlineStr"/>
+      <c r="K100" s="11" t="inlineStr"/>
+      <c r="L100" s="11" t="inlineStr">
+        <is>
+          <t>(229) 377-3701</t>
+        </is>
+      </c>
+      <c r="M100" s="11" t="inlineStr"/>
+      <c r="N100" s="11" t="inlineStr"/>
+      <c r="O100" s="12" t="inlineStr"/>
+      <c r="P100" s="11" t="inlineStr">
+        <is>
+          <t>https://grady.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q100" s="12" t="inlineStr">
+        <is>
+          <t>Serves 4,463 students with 7 schools. PreK offered at Whigham and Shiver Elementary schools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>Greene County School District</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>1302490</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Greene</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>1866</v>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>1 Tiger Path, Greensboro, GA 30642</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr"/>
+      <c r="H101" s="9" t="inlineStr"/>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>Preschool Director</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="inlineStr"/>
+      <c r="K101" s="9" t="inlineStr"/>
+      <c r="L101" s="9" t="inlineStr"/>
+      <c r="M101" s="9" t="inlineStr"/>
+      <c r="N101" s="9" t="inlineStr"/>
+      <c r="O101" s="10" t="inlineStr">
+        <is>
+          <t>Accreditation | Greene County Pre-K program earned 348 on Cognia 2025 accreditation review, above state average | news reports | 2025</t>
+        </is>
+      </c>
+      <c r="P101" s="9" t="inlineStr">
+        <is>
+          <t>https://greene.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q101" s="10" t="inlineStr">
+        <is>
+          <t>Preschool Director role identified but recently transitioned to Assistant Principal position at Greene County Elementary. Pre-K program shows strong performance with recent Cognia accreditation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>Harris County School District</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>1302700</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>5617</v>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>132 Barnes Mill Road, Hamilton, GA 31811</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr"/>
+      <c r="H102" s="11" t="inlineStr"/>
+      <c r="I102" s="11" t="inlineStr"/>
+      <c r="J102" s="11" t="inlineStr"/>
+      <c r="K102" s="11" t="inlineStr"/>
+      <c r="L102" s="11" t="inlineStr">
+        <is>
+          <t>(706) 628-4206</t>
+        </is>
+      </c>
+      <c r="M102" s="11" t="inlineStr"/>
+      <c r="N102" s="11" t="inlineStr"/>
+      <c r="O102" s="12" t="inlineStr"/>
+      <c r="P102" s="11" t="inlineStr">
+        <is>
+          <t>https://harris.k12.ga.us/departments/support-services/pre-k</t>
+        </is>
+      </c>
+      <c r="Q102" s="12" t="inlineStr">
+        <is>
+          <t>Dedicated Pre-K department page exists. Curriculum &amp; Instruction dept handles PreK program development.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>Heard County School District</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>1302790</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>Heard</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="n">
+        <v>2111</v>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>4535 US Highway 27 North, Franklin, GA 30217</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr"/>
+      <c r="I103" s="9" t="inlineStr"/>
+      <c r="J103" s="9" t="inlineStr"/>
+      <c r="K103" s="9" t="inlineStr"/>
+      <c r="L103" s="9" t="inlineStr">
+        <is>
+          <t>(706) 675-3320</t>
+        </is>
+      </c>
+      <c r="M103" s="9" t="inlineStr"/>
+      <c r="N103" s="9" t="inlineStr"/>
+      <c r="O103" s="10" t="inlineStr"/>
+      <c r="P103" s="9" t="inlineStr">
+        <is>
+          <t>https://heard.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q103" s="10" t="inlineStr">
+        <is>
+          <t>PreK offered at three elementary schools (Heard, Centralhatchee, Ephesus). Top 20% of GA districts for performance metrics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>Jeff Davis County School District</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>1303000</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>Jeff Davis</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="n">
+        <v>3077</v>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>1 Tiger Drive, Hazlehurst, GA 31539</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr"/>
+      <c r="H104" s="11" t="inlineStr"/>
+      <c r="I104" s="11" t="inlineStr"/>
+      <c r="J104" s="11" t="inlineStr"/>
+      <c r="K104" s="11" t="inlineStr"/>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>(912) 699-7009</t>
+        </is>
+      </c>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>Into Reading by Houghton Mifflin Harcourt (K-5); Eureka Mathematics by Great Minds (K-5)</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr"/>
+      <c r="O104" s="12" t="inlineStr"/>
+      <c r="P104" s="11" t="inlineStr">
+        <is>
+          <t>https://jeff-davis.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q104" s="12" t="inlineStr">
+        <is>
+          <t>Dedicated Jeff Davis Pre-Kindergarten School serves 154 students. Into Reading and Eureka Mathematics adopted for K-5. 57.7% economically disadvantaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>Jefferson County School District</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>1303060</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Jefferson</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="n">
+        <v>2034</v>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>116 Jones Street, Louisville, GA 30434</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>Beckwith</t>
+        </is>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>Director of Early Learning</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>annette.beckwith@jeffcityschools.org</t>
+        </is>
+      </c>
+      <c r="K105" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L105" s="9" t="inlineStr"/>
+      <c r="M105" s="9" t="inlineStr"/>
+      <c r="N105" s="9" t="inlineStr"/>
+      <c r="O105" s="10" t="inlineStr"/>
+      <c r="P105" s="9" t="inlineStr">
+        <is>
+          <t>https://jefferson.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q105" s="10" t="inlineStr">
+        <is>
+          <t>Director of Early Learning identified with confirmed email. District has Center for Early Learning program. 80% minority enrollment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>Jones County School District</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>1303150</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>4994</v>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>102 South Ennis Avenue, Gray, GA 31032</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr"/>
+      <c r="H106" s="11" t="inlineStr"/>
+      <c r="I106" s="11" t="inlineStr"/>
+      <c r="J106" s="11" t="inlineStr"/>
+      <c r="K106" s="11" t="inlineStr"/>
+      <c r="L106" s="11" t="inlineStr"/>
+      <c r="M106" s="11" t="inlineStr"/>
+      <c r="N106" s="11" t="inlineStr"/>
+      <c r="O106" s="12" t="inlineStr"/>
+      <c r="P106" s="11" t="inlineStr">
+        <is>
+          <t>https://prek.jones.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q106" s="12" t="inlineStr">
+        <is>
+          <t>Dedicated Jones County Pre-K website exists. Pre-K program serves 220 students in Gray, GA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>Lincoln County School District</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>1303330</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>1247</v>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>423 Metasville Road, Lincolnton, GA 30817</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr"/>
+      <c r="I107" s="9" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr"/>
+      <c r="K107" s="9" t="inlineStr"/>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>(706) 359-3742</t>
+        </is>
+      </c>
+      <c r="M107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr"/>
+      <c r="O107" s="10" t="inlineStr"/>
+      <c r="P107" s="9" t="inlineStr">
+        <is>
+          <t>https://lincolncountyschools.org/</t>
+        </is>
+      </c>
+      <c r="Q107" s="10" t="inlineStr">
+        <is>
+          <t>Small district with 1,247 students and 3 schools (elementary, middle, high). PreK offered at Lincoln County Elementary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>McIntosh County School District</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>1303600</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>McIntosh</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>1325</v>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>1100b Ca Devillars, Darien, GA 31305</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr"/>
+      <c r="H108" s="11" t="inlineStr"/>
+      <c r="I108" s="11" t="inlineStr"/>
+      <c r="J108" s="11" t="inlineStr"/>
+      <c r="K108" s="11" t="inlineStr"/>
+      <c r="L108" s="11" t="inlineStr"/>
+      <c r="M108" s="11" t="inlineStr"/>
+      <c r="N108" s="11" t="inlineStr"/>
+      <c r="O108" s="12" t="inlineStr"/>
+      <c r="P108" s="11" t="inlineStr">
+        <is>
+          <t>https://mcintosh.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q108" s="12" t="inlineStr">
+        <is>
+          <t>PreK offered at Todd-Grant Elementary (PreK-5). Curriculum &amp; Instruction page shows comprehensive curriculum development.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>Mitchell County School District</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>1303690</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>108 South Harney Street, Camilla, GA 31730</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>Ashlee</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>Haynes</t>
+        </is>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>Director of Curriculum and Instruction (PreK-8)</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr"/>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>(229) 336-2100</t>
+        </is>
+      </c>
+      <c r="M109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr"/>
+      <c r="O109" s="10" t="inlineStr"/>
+      <c r="P109" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mitchell.k12.ga.us/apps/staff/</t>
+        </is>
+      </c>
+      <c r="Q109" s="10" t="inlineStr">
+        <is>
+          <t>Ashlee Haynes oversees PreK-8 curriculum; director email not publicly listed on website. Email needed — check Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>Montgomery County School District</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>1303750</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>912</v>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>305 South Richardson Street, Mount Vernon, GA 30445</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr"/>
+      <c r="H110" s="11" t="inlineStr"/>
+      <c r="I110" s="11" t="inlineStr"/>
+      <c r="J110" s="11" t="inlineStr"/>
+      <c r="K110" s="11" t="inlineStr"/>
+      <c r="L110" s="11" t="inlineStr">
+        <is>
+          <t>(912) 583-2740</t>
+        </is>
+      </c>
+      <c r="M110" s="11" t="inlineStr"/>
+      <c r="N110" s="11" t="inlineStr"/>
+      <c r="O110" s="12" t="inlineStr"/>
+      <c r="P110" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mcboe.net/</t>
+        </is>
+      </c>
+      <c r="Q110" s="12" t="inlineStr">
+        <is>
+          <t>Small rural district; no dedicated ECE director identified; contact superintendent for PreK information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>Oglethorpe County School District</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>1303990</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Oglethorpe</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="n">
+        <v>2298</v>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>735 Athens Road, Lexington, GA 30648</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
+      <c r="I111" s="9" t="inlineStr"/>
+      <c r="J111" s="9" t="inlineStr"/>
+      <c r="K111" s="9" t="inlineStr"/>
+      <c r="L111" s="9" t="inlineStr">
+        <is>
+          <t>(706) 743-8128</t>
+        </is>
+      </c>
+      <c r="M111" s="9" t="inlineStr"/>
+      <c r="N111" s="9" t="inlineStr"/>
+      <c r="O111" s="10" t="inlineStr"/>
+      <c r="P111" s="9" t="inlineStr">
+        <is>
+          <t>https://www.oglethorpe.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q111" s="10" t="inlineStr">
+        <is>
+          <t>Department of Teaching and Learning oversees PreK; specific ECE director not identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>Pike County School District</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>1304170</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>Pike</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>3498</v>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>16 Jackson Street, Zebulon, GA 30295</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr"/>
+      <c r="H112" s="11" t="inlineStr"/>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>Director of Teaching &amp; Learning</t>
+        </is>
+      </c>
+      <c r="J112" s="11" t="inlineStr"/>
+      <c r="K112" s="11" t="inlineStr"/>
+      <c r="L112" s="11" t="inlineStr">
+        <is>
+          <t>(770) 567-8489</t>
+        </is>
+      </c>
+      <c r="M112" s="11" t="inlineStr"/>
+      <c r="N112" s="11" t="inlineStr"/>
+      <c r="O112" s="12" t="inlineStr"/>
+      <c r="P112" s="11" t="inlineStr">
+        <is>
+          <t>https://pike.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q112" s="12" t="inlineStr">
+        <is>
+          <t>PreK programs at Pike County Primary School; Director of Teaching &amp; Learning title identified but name not confirmed. Email needed — check Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>Pulaski County School District</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>1304220</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>Pulaski</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>1341</v>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>72 Warren Street, Hawkinsville, GA 31036</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr"/>
+      <c r="H113" s="9" t="inlineStr"/>
+      <c r="I113" s="9" t="inlineStr"/>
+      <c r="J113" s="9" t="inlineStr"/>
+      <c r="K113" s="9" t="inlineStr"/>
+      <c r="L113" s="9" t="inlineStr">
+        <is>
+          <t>(478) 783-2287</t>
+        </is>
+      </c>
+      <c r="M113" s="9" t="inlineStr">
+        <is>
+          <t>L.I.T.T.L.E. Children Growing PreK</t>
+        </is>
+      </c>
+      <c r="N113" s="9" t="inlineStr"/>
+      <c r="O113" s="10" t="inlineStr"/>
+      <c r="P113" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pulaski.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q113" s="10" t="inlineStr">
+        <is>
+          <t>District operates L.I.T.T.L.E. Children Growing PreK program; specific ECE director not identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>Stewart County School District</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>1304590</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>364</v>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>7168 Green Grove Road, Lumpkin, GA 31815</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr"/>
+      <c r="H114" s="11" t="inlineStr"/>
+      <c r="I114" s="11" t="inlineStr"/>
+      <c r="J114" s="11" t="inlineStr"/>
+      <c r="K114" s="11" t="inlineStr"/>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>(229) 838-4329</t>
+        </is>
+      </c>
+      <c r="M114" s="11" t="inlineStr"/>
+      <c r="N114" s="11" t="inlineStr"/>
+      <c r="O114" s="12" t="inlineStr"/>
+      <c r="P114" s="11" t="inlineStr">
+        <is>
+          <t>https://www.stewart.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q114" s="12" t="inlineStr">
+        <is>
+          <t>Very small rural district (364 students); no dedicated ECE director identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>Taliaferro County School District</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>1304680</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>Taliaferro</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="n">
+        <v>184</v>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>557 Broad Street NW, Crawfordville, GA 30631</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr"/>
+      <c r="H115" s="9" t="inlineStr"/>
+      <c r="I115" s="9" t="inlineStr"/>
+      <c r="J115" s="9" t="inlineStr"/>
+      <c r="K115" s="9" t="inlineStr"/>
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>(706) 986-0396</t>
+        </is>
+      </c>
+      <c r="M115" s="9" t="inlineStr"/>
+      <c r="N115" s="9" t="inlineStr"/>
+      <c r="O115" s="10" t="inlineStr"/>
+      <c r="P115" s="9" t="inlineStr">
+        <is>
+          <t>https://www.taliaferro.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q115" s="10" t="inlineStr">
+        <is>
+          <t>Very small rural district (184 students); no dedicated ECE director identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>Terrell County School District</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>1304860</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>Terrell</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="n">
+        <v>961</v>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>761 1st Avenue, Dawson, GA 31743</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr"/>
+      <c r="H116" s="11" t="inlineStr"/>
+      <c r="I116" s="11" t="inlineStr"/>
+      <c r="J116" s="11" t="inlineStr"/>
+      <c r="K116" s="11" t="inlineStr"/>
+      <c r="L116" s="11" t="inlineStr">
+        <is>
+          <t>(229) 995-4425</t>
+        </is>
+      </c>
+      <c r="M116" s="11" t="inlineStr"/>
+      <c r="N116" s="11" t="inlineStr"/>
+      <c r="O116" s="12" t="inlineStr"/>
+      <c r="P116" s="11" t="inlineStr">
+        <is>
+          <t>https://www.terrell.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q116" s="12" t="inlineStr">
+        <is>
+          <t>Small rural district; no dedicated ECE director identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>Toombs County School District</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>1305040</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>Toombs</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="n">
+        <v>3076</v>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>600 Bulldog Road Unit 1, Lyons, GA 30436</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
+      <c r="I117" s="9" t="inlineStr"/>
+      <c r="J117" s="9" t="inlineStr"/>
+      <c r="K117" s="9" t="inlineStr"/>
+      <c r="L117" s="9" t="inlineStr">
+        <is>
+          <t>(912) 526-3141</t>
+        </is>
+      </c>
+      <c r="M117" s="9" t="inlineStr"/>
+      <c r="N117" s="9" t="inlineStr"/>
+      <c r="O117" s="10" t="inlineStr"/>
+      <c r="P117" s="9" t="inlineStr">
+        <is>
+          <t>https://www.toombscountyschools.org/</t>
+        </is>
+      </c>
+      <c r="Q117" s="10" t="inlineStr">
+        <is>
+          <t>Curriculum, Instruction, and Assessment department exists; specific PreK director not identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>Towns County School District</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>1305070</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>Towns</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>67 Lakeview Circle, Hiawassee, GA 30546</t>
+        </is>
+      </c>
+      <c r="G118" s="11" t="inlineStr"/>
+      <c r="H118" s="11" t="inlineStr"/>
+      <c r="I118" s="11" t="inlineStr"/>
+      <c r="J118" s="11" t="inlineStr"/>
+      <c r="K118" s="11" t="inlineStr"/>
+      <c r="L118" s="11" t="inlineStr">
+        <is>
+          <t>(706) 896-2279</t>
+        </is>
+      </c>
+      <c r="M118" s="11" t="inlineStr"/>
+      <c r="N118" s="11" t="inlineStr"/>
+      <c r="O118" s="12" t="inlineStr"/>
+      <c r="P118" s="11" t="inlineStr">
+        <is>
+          <t>https://www.towns.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q118" s="12" t="inlineStr">
+        <is>
+          <t>Small rural mountain district; no dedicated ECE director identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>Treutlen County School District</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>1305100</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>Treutlen</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="n">
+        <v>984</v>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>4313 W Main Street, Soperton, GA 30457</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr"/>
+      <c r="H119" s="9" t="inlineStr"/>
+      <c r="I119" s="9" t="inlineStr"/>
+      <c r="J119" s="9" t="inlineStr"/>
+      <c r="K119" s="9" t="inlineStr"/>
+      <c r="L119" s="9" t="inlineStr">
+        <is>
+          <t>(912) 529-4228</t>
+        </is>
+      </c>
+      <c r="M119" s="9" t="inlineStr"/>
+      <c r="N119" s="9" t="inlineStr"/>
+      <c r="O119" s="10" t="inlineStr"/>
+      <c r="P119" s="9" t="inlineStr">
+        <is>
+          <t>https://www.treutlen.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q119" s="10" t="inlineStr">
+        <is>
+          <t>Small rural district; no dedicated ECE director identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>Turner County School District</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>1305190</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>Turner</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>1189</v>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>423 North Cleveland Street, Ashburn, GA 31714</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr"/>
+      <c r="H120" s="11" t="inlineStr"/>
+      <c r="I120" s="11" t="inlineStr"/>
+      <c r="J120" s="11" t="inlineStr"/>
+      <c r="K120" s="11" t="inlineStr"/>
+      <c r="L120" s="11" t="inlineStr">
+        <is>
+          <t>(229) 567-3338</t>
+        </is>
+      </c>
+      <c r="M120" s="11" t="inlineStr"/>
+      <c r="N120" s="11" t="inlineStr"/>
+      <c r="O120" s="12" t="inlineStr"/>
+      <c r="P120" s="11" t="inlineStr">
+        <is>
+          <t>https://www.turner.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q120" s="12" t="inlineStr">
+        <is>
+          <t>Small rural district; no dedicated ECE director identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>Walker County School District</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>1305370</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="n">
+        <v>8422</v>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>201 South Duke Street, Lafayette, GA 30728</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>Director of Curriculum and Instruction</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>robinsamples@walkerschools.org</t>
+        </is>
+      </c>
+      <c r="K121" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L121" s="9" t="inlineStr">
+        <is>
+          <t>(706) 638-1240</t>
+        </is>
+      </c>
+      <c r="M121" s="9" t="inlineStr">
+        <is>
+          <t>LAUNCH Early Childhood Education (partnership with Georgia Northwestern Technical College)</t>
+        </is>
+      </c>
+      <c r="N121" s="9" t="inlineStr"/>
+      <c r="O121" s="10" t="inlineStr">
+        <is>
+          <t>Program | LAUNCH ECE partnership with Georgia Northwestern Technical College for early childhood education | walkerschools.org | 2024</t>
+        </is>
+      </c>
+      <c r="P121" s="9" t="inlineStr">
+        <is>
+          <t>https://www.walkerschools.org/</t>
+        </is>
+      </c>
+      <c r="Q121" s="10" t="inlineStr">
+        <is>
+          <t>Larger district (8,422 students); Robin Samples is Director of Curriculum and Instruction with confirmed email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>Webster County School District</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>1305580</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>Webster</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>259</v>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>7307 Washington Street, Preston, GA 31824</t>
+        </is>
+      </c>
+      <c r="G122" s="11" t="inlineStr"/>
+      <c r="H122" s="11" t="inlineStr"/>
+      <c r="I122" s="11" t="inlineStr"/>
+      <c r="J122" s="11" t="inlineStr"/>
+      <c r="K122" s="11" t="inlineStr"/>
+      <c r="L122" s="11" t="inlineStr">
+        <is>
+          <t>(229) 828-3315</t>
+        </is>
+      </c>
+      <c r="M122" s="11" t="inlineStr"/>
+      <c r="N122" s="11" t="inlineStr"/>
+      <c r="O122" s="12" t="inlineStr"/>
+      <c r="P122" s="11" t="inlineStr">
+        <is>
+          <t>https://www.websterbobcats.org/</t>
+        </is>
+      </c>
+      <c r="Q122" s="12" t="inlineStr">
+        <is>
+          <t>Very small rural district (259 students); no dedicated ECE director identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>Wilcox County School District</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>1305730</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>Wilcox</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="n">
+        <v>1173</v>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>395 College Street West, Abbeville, GA 31001</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr"/>
+      <c r="H123" s="9" t="inlineStr"/>
+      <c r="I123" s="9" t="inlineStr"/>
+      <c r="J123" s="9" t="inlineStr"/>
+      <c r="K123" s="9" t="inlineStr"/>
+      <c r="L123" s="9" t="inlineStr">
+        <is>
+          <t>(229) 467-2141</t>
+        </is>
+      </c>
+      <c r="M123" s="9" t="inlineStr"/>
+      <c r="N123" s="9" t="inlineStr"/>
+      <c r="O123" s="10" t="inlineStr"/>
+      <c r="P123" s="9" t="inlineStr">
+        <is>
+          <t>https://www.wilcox.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q123" s="10" t="inlineStr">
+        <is>
+          <t>Small rural district; no dedicated ECE director identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>Bremen City School District</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>1300510</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>Haralson</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>2373</v>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>501 Pacific Avenue, Bremen, GA 30110</t>
+        </is>
+      </c>
+      <c r="G124" s="11" t="inlineStr"/>
+      <c r="H124" s="11" t="inlineStr"/>
+      <c r="I124" s="11" t="inlineStr"/>
+      <c r="J124" s="11" t="inlineStr"/>
+      <c r="K124" s="11" t="inlineStr"/>
+      <c r="L124" s="11" t="inlineStr">
+        <is>
+          <t>(770) 537-5508</t>
+        </is>
+      </c>
+      <c r="M124" s="11" t="inlineStr"/>
+      <c r="N124" s="11" t="inlineStr"/>
+      <c r="O124" s="12" t="inlineStr"/>
+      <c r="P124" s="11" t="inlineStr">
+        <is>
+          <t>https://www.bremencs.com/</t>
+        </is>
+      </c>
+      <c r="Q124" s="12" t="inlineStr">
+        <is>
+          <t>District operates 4 schools (PK-12). No dedicated ECE director identified on public website. Contact main office for PreK curriculum details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>Buford City School District</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>1300600</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>Gwinnett</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="n">
+        <v>5946</v>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>2625 Sawnee Avenue, Buford, GA 30518</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr"/>
+      <c r="H125" s="9" t="inlineStr"/>
+      <c r="I125" s="9" t="inlineStr"/>
+      <c r="J125" s="9" t="inlineStr"/>
+      <c r="K125" s="9" t="inlineStr"/>
+      <c r="L125" s="9" t="inlineStr"/>
+      <c r="M125" s="9" t="inlineStr"/>
+      <c r="N125" s="9" t="inlineStr"/>
+      <c r="O125" s="10" t="inlineStr"/>
+      <c r="P125" s="9" t="inlineStr">
+        <is>
+          <t>https://www.bufordcityschools.org/</t>
+        </is>
+      </c>
+      <c r="Q125" s="10" t="inlineStr">
+        <is>
+          <t>District operates 5 schools with Early Childhood Program through Special Education &amp; Student Services department. No dedicated ECE director contact found. See bufordcityschools.org for staff directory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>Carrollton City School District</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>1300870</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>Carroll</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>5752</v>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>401 Ben Scott Boulevard, Carrollton, GA 30117</t>
+        </is>
+      </c>
+      <c r="G126" s="11" t="inlineStr"/>
+      <c r="H126" s="11" t="inlineStr"/>
+      <c r="I126" s="11" t="inlineStr"/>
+      <c r="J126" s="11" t="inlineStr"/>
+      <c r="K126" s="11" t="inlineStr"/>
+      <c r="L126" s="11" t="inlineStr">
+        <is>
+          <t>(770) 832-2120</t>
+        </is>
+      </c>
+      <c r="M126" s="11" t="inlineStr"/>
+      <c r="N126" s="11" t="inlineStr"/>
+      <c r="O126" s="12" t="inlineStr">
+        <is>
+          <t>STEM certification | K-3 STEM-certified school as of 2013 | carrolltoncityschools.net | 2013</t>
+        </is>
+      </c>
+      <c r="P126" s="11" t="inlineStr">
+        <is>
+          <t>https://www.carrolltoncityschools.net/</t>
+        </is>
+      </c>
+      <c r="Q126" s="12" t="inlineStr">
+        <is>
+          <t>K-12 STEM focus district with strong arts integration. PreK program housed at Carrollton Elementary. No specific PreK curriculum identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>Chickamauga City School District</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>1301140</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="n">
+        <v>1384</v>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>402 Cove Road, Chickamauga, GA 30707</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr"/>
+      <c r="H127" s="9" t="inlineStr"/>
+      <c r="I127" s="9" t="inlineStr"/>
+      <c r="J127" s="9" t="inlineStr"/>
+      <c r="K127" s="9" t="inlineStr"/>
+      <c r="L127" s="9" t="inlineStr">
+        <is>
+          <t>(706) 382-3100</t>
+        </is>
+      </c>
+      <c r="M127" s="9" t="inlineStr"/>
+      <c r="N127" s="9" t="inlineStr"/>
+      <c r="O127" s="10" t="inlineStr">
+        <is>
+          <t>School-based mental health services | Partnership with Georgia Hope for early intervention mental health services recognized as state model | chickamauga.k12.ga.us | 2023</t>
+        </is>
+      </c>
+      <c r="P127" s="9" t="inlineStr">
+        <is>
+          <t>https://www.glschools.org/</t>
+        </is>
+      </c>
+      <c r="Q127" s="10" t="inlineStr">
+        <is>
+          <t>District serves 3 schools (PK-12). Strong focus on physical, social, and emotional development. No ECE director identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>Commerce City School District</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>1301440</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>1868</v>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>270 Lakeview Drive, Commerce, GA 30529</t>
+        </is>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>Sandy</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>Metts</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>Curriculum Director</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="inlineStr"/>
+      <c r="K128" s="11" t="inlineStr"/>
+      <c r="L128" s="11" t="inlineStr">
+        <is>
+          <t>(706) 335-5500</t>
+        </is>
+      </c>
+      <c r="M128" s="11" t="inlineStr"/>
+      <c r="N128" s="11" t="inlineStr"/>
+      <c r="O128" s="12" t="inlineStr"/>
+      <c r="P128" s="11" t="inlineStr">
+        <is>
+          <t>https://www.commercecityschools.org/</t>
+        </is>
+      </c>
+      <c r="Q128" s="12" t="inlineStr">
+        <is>
+          <t>District operates 4 schools. Sandy Metts is Curriculum Director (may oversee PreK curriculum decisions). Top-rated district (10/10 testing ranking in GA top 10%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>Dublin City School District</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>1301870</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>Laurens</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr"/>
+      <c r="F129" s="9" t="inlineStr"/>
+      <c r="G129" s="9" t="inlineStr"/>
+      <c r="H129" s="9" t="inlineStr"/>
+      <c r="I129" s="9" t="inlineStr"/>
+      <c r="J129" s="9" t="inlineStr"/>
+      <c r="K129" s="9" t="inlineStr"/>
+      <c r="L129" s="9" t="inlineStr"/>
+      <c r="M129" s="9" t="inlineStr"/>
+      <c r="N129" s="9" t="inlineStr"/>
+      <c r="O129" s="10" t="inlineStr">
+        <is>
+          <t>Charter System of the Year | Award recipient: Georgia's 2019 Charter System of the Year | dcsirish.com | 2019 | Exemplary Board Status Award | Consistent recipient (2015-present) | Georgia School Boards Association | Ongoing | High graduation rate | 95.5% graduation rate with Community Eligibility Provision (no-cost meals for all students) | dcsirish.com | Current</t>
+        </is>
+      </c>
+      <c r="P129" s="9" t="inlineStr">
+        <is>
+          <t>https://www.dcsirish.com/</t>
+        </is>
+      </c>
+      <c r="Q129" s="10" t="inlineStr">
+        <is>
+          <t>District operates 5 schools (PK-12) as charter system. Dedicated preschool program with own website (preschool.dublinschools.net). No ECE director contact found on public website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>Pelham City School District</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>1304080</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F130" s="11" t="inlineStr"/>
+      <c r="G130" s="11" t="inlineStr"/>
+      <c r="H130" s="11" t="inlineStr"/>
+      <c r="I130" s="11" t="inlineStr"/>
+      <c r="J130" s="11" t="inlineStr"/>
+      <c r="K130" s="11" t="inlineStr"/>
+      <c r="L130" s="11" t="inlineStr"/>
+      <c r="M130" s="11" t="inlineStr"/>
+      <c r="N130" s="11" t="inlineStr"/>
+      <c r="O130" s="12" t="inlineStr"/>
+      <c r="P130" s="11" t="inlineStr">
+        <is>
+          <t>https://www.pelham-city.k12.ga.us/</t>
+        </is>
+      </c>
+      <c r="Q130" s="12" t="inlineStr">
+        <is>
+          <t>District operates 3 schools (PK-12) as charter system. Pelham Elementary serves PK-5 (608 students). No ECE director identified. Limited public contact information online.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>Social Circle City School District</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>1304540</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>Walton</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>1942</v>
+      </c>
+      <c r="F131" s="9" t="inlineStr"/>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>Lindsey</t>
+        </is>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>Coleman</t>
+        </is>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>Director of Curriculum and Instruction K-6</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>lindsey.coleman@socialcircleschools.org</t>
+        </is>
+      </c>
+      <c r="K131" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L131" s="9" t="inlineStr">
+        <is>
+          <t>(770) 464-2731</t>
+        </is>
+      </c>
+      <c r="M131" s="9" t="inlineStr">
+        <is>
+          <t>Frog Street</t>
+        </is>
+      </c>
+      <c r="N131" s="9" t="inlineStr"/>
+      <c r="O131" s="10" t="inlineStr"/>
+      <c r="P131" s="9" t="inlineStr">
+        <is>
+          <t>https://www.socialcircleschools.com/departments/curriculum-and-instruction</t>
+        </is>
+      </c>
+      <c r="Q131" s="10" t="inlineStr">
+        <is>
+          <t>PreK program uses state-approved Frog Street curriculum with Heggerty and Fundations (phonics/phonemic awareness). Georgia Pre-K serves 4-year-olds; spots filled by lottery with district priority. Lindsey Coleman oversees K-6 curriculum which includes PreK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>Trion City School District</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>1305130</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>Chattooga</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="n">
+        <v>1313</v>
+      </c>
+      <c r="F132" s="11" t="inlineStr"/>
+      <c r="G132" s="11" t="inlineStr"/>
+      <c r="H132" s="11" t="inlineStr"/>
+      <c r="I132" s="11" t="inlineStr"/>
+      <c r="J132" s="11" t="inlineStr"/>
+      <c r="K132" s="11" t="inlineStr"/>
+      <c r="L132" s="11" t="inlineStr"/>
+      <c r="M132" s="11" t="inlineStr"/>
+      <c r="N132" s="11" t="inlineStr"/>
+      <c r="O132" s="12" t="inlineStr"/>
+      <c r="P132" s="11" t="inlineStr">
+        <is>
+          <t>https://www.trionschools.org/</t>
+        </is>
+      </c>
+      <c r="Q132" s="12" t="inlineStr">
+        <is>
+          <t>District operates 3 schools (PK-12). PreK program references Georgia Early Learning and Development Standards (GELDS) framework. No specific curriculum brand identified. No ECE director contact found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>Valdosta City School District</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>1305310</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>Lowndes</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr"/>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>1204 Williams Street, Valdosta, GA 31602</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>David Cole</t>
+        </is>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>Assistant Superintendent of Teaching &amp; Learning &amp; K-12 Social Studies</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="inlineStr"/>
+      <c r="K133" s="9" t="inlineStr"/>
+      <c r="L133" s="9" t="inlineStr">
+        <is>
+          <t>(229) 671-6064</t>
+        </is>
+      </c>
+      <c r="M133" s="9" t="inlineStr"/>
+      <c r="N133" s="9" t="inlineStr"/>
+      <c r="O133" s="10" t="inlineStr"/>
+      <c r="P133" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gocats.org/apps/pages/index.jsp?uREC_ID=335691&amp;type=d&amp;pREC_ID=743398</t>
+        </is>
+      </c>
+      <c r="Q133" s="10" t="inlineStr">
+        <is>
+          <t>Large district with 8 schools. Dr. David Cole oversees Teaching &amp; Learning (may coordinate ECE curriculum). Additional curriculum directors available for specific subjects (ELA, Math, Fine Arts). PreK curriculum not identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>Vidalia City School District</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>1305340</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>Toombs</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="n">
+        <v>2366</v>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>301 Adams Street, Vidalia, GA 30474</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr"/>
+      <c r="H134" s="11" t="inlineStr"/>
+      <c r="I134" s="11" t="inlineStr"/>
+      <c r="J134" s="11" t="inlineStr"/>
+      <c r="K134" s="11" t="inlineStr"/>
+      <c r="L134" s="11" t="inlineStr">
+        <is>
+          <t>(912) 537-7931</t>
+        </is>
+      </c>
+      <c r="M134" s="11" t="inlineStr"/>
+      <c r="N134" s="11" t="inlineStr"/>
+      <c r="O134" s="12" t="inlineStr"/>
+      <c r="P134" s="11" t="inlineStr">
+        <is>
+          <t>https://vidaliacity.schoolinsites.com/</t>
+        </is>
+      </c>
+      <c r="Q134" s="12" t="inlineStr">
+        <is>
+          <t>District operates 4 schools (PK-12). PreK housed at J.D. Dickerson Primary School (PK-1). Focus on language-rich adult-child interactions for brain development. No specific curriculum identified.</t>
         </is>
       </c>
     </row>
